--- a/docs/BANG_KIEM_THU_VA_FIX_LOI_SMARTLIB.xlsx
+++ b/docs/BANG_KIEM_THU_VA_FIX_LOI_SMARTLIB.xlsx
@@ -644,7 +644,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2329,7 +2329,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -3741,7 +3741,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>

--- a/docs/BANG_KIEM_THU_VA_FIX_LOI_SMARTLIB.xlsx
+++ b/docs/BANG_KIEM_THU_VA_FIX_LOI_SMARTLIB.xlsx
@@ -666,7 +666,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tự động hóa 100% trong test_evaluation.py (Thời gian chạy: 1.47 giây | Tỷ lệ thành công: 40/40 PASS - 100%)</t>
+          <t>Lớp: KTPM K23B | Nhóm SV: Vũ Hồng Dũng (Trưởng nhóm - DTC245180068), Nguyễn Trung Học (DTC245180174), Lê Quang Hưng (DTC245180036)</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dành cho đội ngũ Backend, Frontend, DevOps đối chiếu nguyên nhân và cách xử lý trong mã nguồn</t>
+          <t>Lớp: KTPM K23B | Nhóm SV: Vũ Hồng Dũng (Trưởng nhóm - DTC245180068), Nguyễn Trung Học (DTC245180174), Lê Quang Hưng (DTC245180036)</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dành cho sinh viên thực hành thao tác trên http://localhost:3000 để ghi điểm trọn vẹn trước Hội đồng chấm thi</t>
+          <t>Lớp: KTPM K23B | Nhóm SV: Vũ Hồng Dũng (Trưởng nhóm - DTC245180068), Nguyễn Trung Học (DTC245180174), Lê Quang Hưng (DTC245180036)</t>
         </is>
       </c>
     </row>
